--- a/school_surveys/026_parent_school_program_preference_poll_form--school_surveys.xlsx
+++ b/school_surveys/026_parent_school_program_preference_poll_form--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>parent_school_program_preference_poll_form</t>
+          <t>parent_child_interests</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Parent Program Preference Poll Form</t>
+          <t>What are your child's interests?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>parent_program_preferences</t>
+          <t>parent_program_priority</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Parent Program Preferences</t>
+          <t>What kind of programs do you think are most important for our school?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>program_preferences</t>
+          <t>parent_participation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Program Preferences</t>
+          <t>Have you participated in any of our programs?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>new_program</t>
+          <t>support_priority</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New Program</t>
+          <t>What is your priority for support?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ongoing_data_collection</t>
+          <t>support_data_collection</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ongoing Data Collection</t>
+          <t>Do you need help with data collection?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>priority_improvements</t>
+          <t>support_data_collection_input</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Priority Improvements</t>
+          <t>Do you want to support data collection?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>k12_teams</t>
+          <t>parent_form_submission</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K-12 Teams</t>
+          <t>How do you want to submit your input?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>parent_programs</t>
+          <t>submission_priority</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Parent Programs</t>
+          <t>How important is it for you to have organized form submissions?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>organized_form_submissions</t>
+          <t>submission_tools</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Organized Form Submissions</t>
+          <t>What tools are you comfortable using for form submissions?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jotform</t>
+          <t>other_programs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jotform</t>
+          <t>Do you have any other programs that you would like to be implemented?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>school_programs</t>
+          <t>school_program_priority</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>School Programs</t>
+          <t>What is your priority for our school program?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>school_programs_priority</t>
+          <t>support_teams</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>School Programs Priority</t>
+          <t>Do you need help with support teams?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parent_school_programs</t>
+          <t>support_teams_input</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Parent School Programs</t>
+          <t>Do you want to support our support teams?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>support_teams</t>
+          <t>data_collection_importance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Support Teams</t>
+          <t>How important is ongoing data collection to you?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>support_teams_priority</t>
+          <t>data_collection_input</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Support Teams Priority</t>
+          <t>Do you want to provide input on ongoing data collection?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>support_ongoing_data_collection</t>
+          <t>input_submission</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Support Ongoing Data Collection</t>
+          <t>Input Submission</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>support_parent_input</t>
+          <t>involved</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Support Parent Input</t>
+          <t>Do you want to be involved in our program?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>help</t>
+          <t>submission_help</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Do you need help with submitting?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,833 +965,782 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>parent_program_preferences_choices</t>
+          <t>parent_child_interests_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>parent_program_preferences_choices</t>
+          <t>parent_child_interests_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>parent_program_preferences_choices</t>
+          <t>parent_child_interests_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>program_preferences_choices</t>
+          <t>parent_program_priority_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>program_preferences_choices</t>
+          <t>parent_program_priority_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>program_preferences_choices</t>
+          <t>parent_program_priority_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>new_program_choices</t>
+          <t>parent_participation_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>new_program_choices</t>
+          <t>parent_participation_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>priority_improvements_choices</t>
+          <t>support_priority_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>priority_improvements_choices</t>
+          <t>support_priority_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>priority_improvements_choices</t>
+          <t>support_priority_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>k12_teams_choices</t>
+          <t>support_data_collection_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>k12_teams_choices</t>
+          <t>support_data_collection_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>k12_teams_choices</t>
+          <t>support_data_collection_input_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>parent_programs_choices</t>
+          <t>support_data_collection_input_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>parent_programs_choices</t>
+          <t>parent_form_submission_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>parent_programs_choices</t>
+          <t>parent_form_submission_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>jotform_choices</t>
+          <t>parent_form_submission_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>jotform_choices</t>
+          <t>submission_priority_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jotform_choices</t>
+          <t>submission_priority_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>school_programs_choices</t>
+          <t>submission_priority_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>school_programs_choices</t>
+          <t>submission_tools_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>school_programs_priority_choices</t>
+          <t>submission_tools_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>school_programs_priority_choices</t>
+          <t>submission_tools_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>school_programs_priority_choices</t>
+          <t>other_programs_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>parent_school_programs_choices</t>
+          <t>other_programs_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>parent_school_programs_choices</t>
+          <t>other_programs_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>support_teams_choices</t>
+          <t>school_program_priority_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>support_teams_choices</t>
+          <t>school_program_priority_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>support_teams_choices</t>
+          <t>school_program_priority_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>support_teams_priority_choices</t>
+          <t>support_teams_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>support_teams_priority_choices</t>
+          <t>support_teams_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>support_ongoing_data_collection_choices</t>
+          <t>support_teams_input_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>support_ongoing_data_collection_choices</t>
+          <t>support_teams_input_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>support_ongoing_data_collection_choices</t>
+          <t>data_collection_importance_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>support_parent_input_choices</t>
+          <t>data_collection_importance_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>support_parent_input_choices</t>
+          <t>data_collection_importance_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>report_choices</t>
+          <t>data_collection_input_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>report_choices</t>
+          <t>data_collection_input_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>input_submission_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>input_submission_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>input_submission_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>involved_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>involved_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>submission_help_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>submission_help_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
